--- a/Horarios/Colectivos/136-Rapido/LaboralPrimeraJunta.xlsx
+++ b/Horarios/Colectivos/136-Rapido/LaboralPrimeraJunta.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>739_43391-1</t>
+          <t>739_43380-1</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -519,7 +519,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>739_43392-1</t>
+          <t>739_43381-1</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>739_43393-1</t>
+          <t>739_43382-1</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -561,7 +561,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>739_43394-1</t>
+          <t>739_43383-1</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -582,7 +582,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>739_43395-1</t>
+          <t>739_43384-1</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>739_43396-1</t>
+          <t>739_43385-1</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>739_43397-1</t>
+          <t>739_43386-1</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -645,7 +645,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>739_43398-1</t>
+          <t>739_43387-1</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -666,7 +666,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>739_43399-1</t>
+          <t>739_43388-1</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>739_43400-1</t>
+          <t>739_43389-1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>739_43401-1</t>
+          <t>739_43390-1</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -729,7 +729,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>739_43402-1</t>
+          <t>739_43391-1</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>739_43403-1</t>
+          <t>739_43392-1</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>739_43404-1</t>
+          <t>739_43393-1</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -788,7 +788,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>739_43405-1</t>
+          <t>739_43394-1</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -809,7 +809,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>739_43406-1</t>
+          <t>739_43395-1</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -824,11 +824,11 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46259</v>
+        <v>46266</v>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>739_43407-1</t>
+          <t>739_43396-1</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>739_43408-1</t>
+          <t>739_43397-1</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -870,7 +870,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>739_43409-1</t>
+          <t>739_43398-1</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>739_43410-1</t>
+          <t>739_43399-1</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
